--- a/artfynd/A 8858-2024 artfynd.xlsx
+++ b/artfynd/A 8858-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137378863</v>
       </c>
       <c r="B2" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137378872</v>
       </c>
       <c r="B3" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137378862</v>
       </c>
       <c r="B4" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,48 +1016,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137378868</v>
+        <v>137378854</v>
       </c>
       <c r="B5" t="n">
-        <v>92542</v>
+        <v>92585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1505</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Välivaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>852575</v>
+        <v>852806</v>
       </c>
       <c r="R5" t="n">
-        <v>7461850</v>
+        <v>7461782</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1089,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,16 +1096,15 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1126,16 +1122,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137378868</t>
+          <t>https://artportalen.se/Sighting/137378854</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137378854</v>
+        <v>137378869</v>
       </c>
       <c r="B6" t="n">
-        <v>92581</v>
+        <v>92585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>852806</v>
+        <v>852647</v>
       </c>
       <c r="R6" t="n">
-        <v>7461782</v>
+        <v>7461752</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1202,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,16 +1234,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137378854</t>
+          <t>https://artportalen.se/Sighting/137378869</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137378869</v>
+        <v>137378855</v>
       </c>
       <c r="B7" t="n">
-        <v>92581</v>
+        <v>92152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>852647</v>
+        <v>852795</v>
       </c>
       <c r="R7" t="n">
-        <v>7461752</v>
+        <v>7461776</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1314,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,38 +1346,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137378869</t>
+          <t>https://artportalen.se/Sighting/137378855</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137378855</v>
+        <v>137378871</v>
       </c>
       <c r="B8" t="n">
-        <v>92148</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>852795</v>
+        <v>852662</v>
       </c>
       <c r="R8" t="n">
-        <v>7461776</v>
+        <v>7461729</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1426,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,38 +1458,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137378855</t>
+          <t>https://artportalen.se/Sighting/137378871</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137378871</v>
+        <v>137378857</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>83530</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>852662</v>
+        <v>852702</v>
       </c>
       <c r="R9" t="n">
-        <v>7461729</v>
+        <v>7461811</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1538,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,16 +1570,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137378871</t>
+          <t>https://artportalen.se/Sighting/137378857</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137378857</v>
+        <v>137378856</v>
       </c>
       <c r="B10" t="n">
-        <v>83526</v>
+        <v>58038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,34 +1587,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Välivaara, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>852702</v>
+        <v>852748</v>
       </c>
       <c r="R10" t="n">
-        <v>7461811</v>
+        <v>7461759</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1650,7 +1647,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1657,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Barkfläk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,16 +1688,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137378857</t>
+          <t>https://artportalen.se/Sighting/137378856</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137378856</v>
+        <v>137378865</v>
       </c>
       <c r="B11" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>852748</v>
+        <v>852587</v>
       </c>
       <c r="R11" t="n">
-        <v>7461759</v>
+        <v>7461938</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1763,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1804,16 +1806,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137378856</t>
+          <t>https://artportalen.se/Sighting/137378865</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137378865</v>
+        <v>137378866</v>
       </c>
       <c r="B12" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,10 +1848,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>852587</v>
+        <v>852571</v>
       </c>
       <c r="R12" t="n">
-        <v>7461938</v>
+        <v>7461913</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1881,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1891,12 +1893,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Barkfläk</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,16 +1924,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137378865</t>
+          <t>https://artportalen.se/Sighting/137378866</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137378866</v>
+        <v>137378867</v>
       </c>
       <c r="B13" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1964,10 +1966,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>852571</v>
+        <v>852573</v>
       </c>
       <c r="R13" t="n">
-        <v>7461913</v>
+        <v>7461857</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1999,7 +2001,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2009,12 +2011,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2040,16 +2037,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137378866</t>
+          <t>https://artportalen.se/Sighting/137378867</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137378867</v>
+        <v>137378873</v>
       </c>
       <c r="B14" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,17 +2072,20 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Välivaara, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>852573</v>
+        <v>852697</v>
       </c>
       <c r="R14" t="n">
-        <v>7461857</v>
+        <v>7461687</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2127,7 +2127,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Barkfläk från födosök</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,16 +2158,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137378867</t>
+          <t>https://artportalen.se/Sighting/137378873</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137378873</v>
+        <v>137378859</v>
       </c>
       <c r="B15" t="n">
-        <v>58035</v>
+        <v>58199</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,38 +2175,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Välivaara, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>852697</v>
+        <v>852700</v>
       </c>
       <c r="R15" t="n">
-        <v>7461687</v>
+        <v>7461835</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2233,7 +2234,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2243,12 +2244,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Barkfläk från födosök</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,16 +2270,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137378873</t>
+          <t>https://artportalen.se/Sighting/137378859</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137378859</v>
+        <v>137378864</v>
       </c>
       <c r="B16" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,16 +2305,17 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Välivaara, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>852700</v>
+        <v>852587</v>
       </c>
       <c r="R16" t="n">
-        <v>7461835</v>
+        <v>7461938</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2350,7 +2347,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2360,7 +2357,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,16 +2383,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137378859</t>
+          <t>https://artportalen.se/Sighting/137378864</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137378864</v>
+        <v>137378870</v>
       </c>
       <c r="B17" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2428,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>852587</v>
+        <v>852647</v>
       </c>
       <c r="R17" t="n">
-        <v>7461938</v>
+        <v>7461752</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2463,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,7 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,119 +2495,6 @@
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137378864</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>137378870</v>
-      </c>
-      <c r="B18" t="n">
-        <v>58196</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Välivaara, Nb</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>852647</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7461752</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Pajala</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Korpilombolo</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137378870</t>
         </is>
@@ -2634,7 +2518,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
